--- a/kronshtatsky/vorKron.xlsx
+++ b/kronshtatsky/vorKron.xlsx
@@ -9,16 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12405" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12405" firstSheet="6" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="1эт" sheetId="2" r:id="rId2"/>
-    <sheet name="2эт" sheetId="4" r:id="rId3"/>
-    <sheet name="3эт" sheetId="5" r:id="rId4"/>
-    <sheet name="СадПол" sheetId="7" r:id="rId5"/>
-    <sheet name="СадОтксы" sheetId="6" r:id="rId6"/>
-    <sheet name="Реестр" sheetId="8" r:id="rId7"/>
+    <sheet name="Лист1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="1эт" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="2эт" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="3эт" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Реестр" sheetId="8" state="hidden" r:id="rId5"/>
+    <sheet name="Расчет" sheetId="10" state="hidden" r:id="rId6"/>
+    <sheet name="СадПол" sheetId="7" r:id="rId7"/>
+    <sheet name="СадОтксы" sheetId="6" r:id="rId8"/>
+    <sheet name="СадСтены" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="116">
   <si>
     <t>высота 3930</t>
   </si>
@@ -339,6 +341,45 @@
   </si>
   <si>
     <t>Пол</t>
+  </si>
+  <si>
+    <t>Количество</t>
+  </si>
+  <si>
+    <t>Имя</t>
+  </si>
+  <si>
+    <t>Цвет</t>
+  </si>
+  <si>
+    <t>Слой</t>
+  </si>
+  <si>
+    <t>Длина</t>
+  </si>
+  <si>
+    <t>Полилиния</t>
+  </si>
+  <si>
+    <t>ПОСЛОЮ</t>
+  </si>
+  <si>
+    <t>0) Дверь 2.1м-</t>
+  </si>
+  <si>
+    <t>0) Стена 3.93м</t>
+  </si>
+  <si>
+    <t>1) Окна 2.25м-</t>
+  </si>
+  <si>
+    <t>0) дверьки 1.8м-</t>
+  </si>
+  <si>
+    <t>Итог</t>
+  </si>
+  <si>
+    <t>Итог, м2.</t>
   </si>
 </sst>
 </file>
@@ -386,7 +427,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -409,11 +450,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -472,6 +526,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2913,728 +2980,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:D66"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="9.140625" style="10"/>
-    <col min="2" max="2" width="9.140625" style="12"/>
-    <col min="3" max="3" width="37.28515625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="12"/>
-    <col min="5" max="16384" width="9.140625" style="10"/>
-  </cols>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B1" s="19">
-        <v>1.59</v>
-      </c>
-      <c r="C1" s="20" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="D1" s="21">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="19">
-        <v>1.6</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="21">
-        <v>87.9</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="19">
-        <v>1.61</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D3" s="21">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="19">
-        <v>1.62</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="21">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="19">
-        <v>1.63</v>
-      </c>
-      <c r="C5" s="20" t="s">
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="D5" s="21">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="19">
-        <v>1.64</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="21">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="19">
-        <v>1.65</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="21">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" s="19">
-        <v>1.66</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="21">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" s="19">
-        <v>1.67</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="21">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="19">
-        <v>1.68</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="21">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="19">
-        <v>1.69</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="21">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="19">
-        <v>1.7</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="21">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="19">
-        <v>1.71</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="21">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="19">
-        <v>1.72</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="21">
-        <v>29.3</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="19">
-        <v>1.73</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="21">
-        <v>50.3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="19">
-        <v>1.74</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="21">
-        <v>55.4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="19">
-        <v>1.75</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="21">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B18" s="19">
-        <v>1.76</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="21">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="19">
-        <v>1.77</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="21">
-        <v>41.2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="19">
-        <v>1.78</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="21">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="18"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="18">
-        <v>2.36</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="18">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="18">
-        <v>2.37</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="18">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="18">
-        <v>2.38</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="18">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="18">
-        <v>2.39</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="18">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="18">
-        <v>2.4</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="18">
-        <v>50.4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="18">
-        <v>2.41</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="18">
-        <v>55.9</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="18">
-        <v>2.42</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="18">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="18">
-        <v>2.4300000000000002</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="18">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="18">
-        <v>2.44</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="18">
-        <v>50.5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" s="18">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="18">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="18">
-        <v>2.46</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="18">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="18">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D33" s="18">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B34" s="18">
-        <v>2.48</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="18">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="18">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="D35" s="18">
-        <v>72.3</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="18">
-        <v>2.5</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="18">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="18">
-        <v>37.6</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="18">
-        <v>2.52</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D38" s="18">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="18">
-        <v>2.5299999999999998</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D39" s="18">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="18">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" s="18">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="18">
-        <v>2.56</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D41" s="18">
-        <v>59.9</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="18">
-        <v>2.57</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="D42" s="18">
-        <v>26.2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="18">
-        <v>2.58</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="18">
-        <v>74.5</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="18"/>
-      <c r="C44" s="16"/>
-      <c r="D44" s="18"/>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="18">
-        <v>3.22</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="18">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="18">
-        <v>3.23</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D46" s="18">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="18">
-        <v>3.24</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D47" s="18">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="18">
-        <v>3.25</v>
-      </c>
-      <c r="C48" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" s="18">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="18">
-        <v>3.26</v>
-      </c>
-      <c r="C49" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="18">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" s="18">
-        <v>3.27</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D50" s="18">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" s="18">
-        <v>3.28</v>
-      </c>
-      <c r="C51" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D51" s="18">
-        <v>23.3</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" s="18">
-        <v>3.29</v>
-      </c>
-      <c r="C52" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="D52" s="18">
-        <v>50.8</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" s="18">
-        <v>3.3</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="18">
-        <v>55.7</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" s="18">
-        <v>3.31</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="D54" s="18">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B55" s="18">
-        <v>3.32</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D55" s="18">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B56" s="18">
-        <v>3.33</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="18">
-        <v>74.599999999999994</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B57" s="18">
-        <v>3.34</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D57" s="18">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="B58" s="18">
-        <v>3.35</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" s="18">
-        <v>74.099999999999994</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="B59" s="18">
-        <v>3.36</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D59" s="18">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B60" s="18">
-        <v>3.37</v>
-      </c>
-      <c r="C60" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D60" s="18">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B61" s="18">
-        <v>3.39</v>
-      </c>
-      <c r="C61" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D61" s="18">
-        <v>6.3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B62" s="18">
-        <v>3.4</v>
-      </c>
-      <c r="C62" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D62" s="18">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B63" s="18">
-        <v>3.41</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D63" s="18">
-        <v>36.4</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B64" s="18">
-        <v>3.42</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D64" s="18">
-        <v>59.7</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B65" s="18">
-        <v>3.44</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D65" s="18">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B66" s="18">
-        <v>3.45</v>
-      </c>
-      <c r="C66" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D66" s="18">
-        <v>82.7</v>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3644,6 +3035,1711 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="I1" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="L1" s="25" t="str">
+        <f>G1</f>
+        <v>0) Стена 3.93м</v>
+      </c>
+      <c r="M1" s="25" t="str">
+        <f>H1</f>
+        <v>1) Окна 2.25м-</v>
+      </c>
+      <c r="N1" s="25" t="str">
+        <f>I1</f>
+        <v>0) Дверь 2.1м-</v>
+      </c>
+      <c r="O1" s="25" t="str">
+        <f>J1</f>
+        <v>0) дверьки 1.8м-</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2">
+        <v>1555</v>
+      </c>
+      <c r="E2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF($E2=G$1,$D2*L$2/1000*$A2, "")</f>
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <f>IF($E2=H$1,$D2*M$2/1000*$A2, "")</f>
+        <v/>
+      </c>
+      <c r="I2">
+        <f>IF($E2=I$1,$D2*N$2/1000*$A2, "")</f>
+        <v>3.2654999999999998</v>
+      </c>
+      <c r="J2" t="str">
+        <f>IF($E2=J$1,$D2*O$2/1000*$A2, "")</f>
+        <v/>
+      </c>
+      <c r="L2" s="25">
+        <v>3.93</v>
+      </c>
+      <c r="M2" s="25">
+        <v>2.25</v>
+      </c>
+      <c r="N2" s="25">
+        <v>2.1</v>
+      </c>
+      <c r="O2" s="25">
+        <v>1.8</v>
+      </c>
+      <c r="P2" s="25"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3">
+        <v>1450</v>
+      </c>
+      <c r="E3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" t="str">
+        <f>IF($E3=G$1,$D3*L$2/1000*$A3, "")</f>
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <f>IF($E3=H$1,$D3*M$2/1000*$A3, "")</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF($E3=I$1,$D3*N$2/1000*$A3, "")</f>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="J3" t="str">
+        <f>IF($E3=J$1,$D3*O$2/1000*$A3, "")</f>
+        <v/>
+      </c>
+      <c r="L3" s="26">
+        <f>SUM(G2:G50)</f>
+        <v>190.91155965000002</v>
+      </c>
+      <c r="M3" s="26">
+        <f>SUM(H2:H50)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="26">
+        <f>SUM(I2:I50)</f>
+        <v>20.275500000000001</v>
+      </c>
+      <c r="O3" s="26">
+        <f>SUM(J2:J50)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="26">
+        <f>ROUND(L3-M3-N3-O3, 2)</f>
+        <v>170.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4">
+        <v>48578.004999999997</v>
+      </c>
+      <c r="E4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4">
+        <f>IF($E4=G$1,$D4*L$2/1000*$A4, "")</f>
+        <v>190.91155965000002</v>
+      </c>
+      <c r="H4" t="str">
+        <f>IF($E4=H$1,$D4*M$2/1000*$A4, "")</f>
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <f>IF($E4=I$1,$D4*N$2/1000*$A4, "")</f>
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <f>IF($E4=J$1,$D4*O$2/1000*$A4, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5">
+        <v>1400</v>
+      </c>
+      <c r="E5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" t="str">
+        <f>IF($E5=G$1,$D5*L$2/1000*$A5, "")</f>
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <f>IF($E5=H$1,$D5*M$2/1000*$A5, "")</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF($E5=I$1,$D5*N$2/1000*$A5, "")</f>
+        <v>2.94</v>
+      </c>
+      <c r="J5" t="str">
+        <f>IF($E5=J$1,$D5*O$2/1000*$A5, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6">
+        <v>1450</v>
+      </c>
+      <c r="E6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" t="str">
+        <f>IF($E6=G$1,$D6*L$2/1000*$A6, "")</f>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <f>IF($E6=H$1,$D6*M$2/1000*$A6, "")</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF($E6=I$1,$D6*N$2/1000*$A6, "")</f>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="J6" t="str">
+        <f>IF($E6=J$1,$D6*O$2/1000*$A6, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7">
+        <v>1450</v>
+      </c>
+      <c r="E7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G7" t="str">
+        <f>IF($E7=G$1,$D7*L$2/1000*$A7, "")</f>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <f>IF($E7=H$1,$D7*M$2/1000*$A7, "")</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF($E7=I$1,$D7*N$2/1000*$A7, "")</f>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="J7" t="str">
+        <f>IF($E7=J$1,$D7*O$2/1000*$A7, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8">
+        <v>1400</v>
+      </c>
+      <c r="E8" t="s">
+        <v>110</v>
+      </c>
+      <c r="G8" t="str">
+        <f>IF($E8=G$1,$D8*L$2/1000*$A8, "")</f>
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <f>IF($E8=H$1,$D8*M$2/1000*$A8, "")</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF($E8=I$1,$D8*N$2/1000*$A8, "")</f>
+        <v>2.94</v>
+      </c>
+      <c r="J8" t="str">
+        <f>IF($E8=J$1,$D8*O$2/1000*$A8, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9">
+        <v>950</v>
+      </c>
+      <c r="E9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" t="str">
+        <f>IF($E9=G$1,$D9*L$2/1000*$A9, "")</f>
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <f>IF($E9=H$1,$D9*M$2/1000*$A9, "")</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF($E9=I$1,$D9*N$2/1000*$A9, "")</f>
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="J9" t="str">
+        <f>IF($E9=J$1,$D9*O$2/1000*$A9, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" t="str">
+        <f>IF($E10=G$1,$D10*L$2/1000*$A10, "")</f>
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <f>IF($E10=H$1,$D10*M$2/1000*$A10, "")</f>
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <f>IF($E10=I$1,$D10*N$2/1000*$A10, "")</f>
+        <v/>
+      </c>
+      <c r="J10">
+        <f>IF($E10=J$1,$D10*O$2/1000*$A10, "")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF($E11=G$1,$D11*L$2/1000*$A11, "")</f>
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <f>IF($E11=H$1,$D11*M$2/1000*$A11, "")</f>
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <f>IF($E11=I$1,$D11*N$2/1000*$A11, "")</f>
+        <v/>
+      </c>
+      <c r="J11">
+        <f>IF($E11=J$1,$D11*O$2/1000*$A11, "")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" t="str">
+        <f>IF($E12=G$1,$D12*L$2/1000*$A12, "")</f>
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <f>IF($E12=H$1,$D12*M$2/1000*$A12, "")</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF($E12=I$1,$D12*N$2/1000*$A12, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" t="str">
+        <f>IF($E12=J$1,$D12*O$2/1000*$A12, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>110</v>
+      </c>
+      <c r="G13" t="str">
+        <f>IF($E13=G$1,$D13*L$2/1000*$A13, "")</f>
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <f>IF($E13=H$1,$D13*M$2/1000*$A13, "")</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF($E13=I$1,$D13*N$2/1000*$A13, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" t="str">
+        <f>IF($E13=J$1,$D13*O$2/1000*$A13, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" t="str">
+        <f>IF($E14=G$1,$D14*L$2/1000*$A14, "")</f>
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <f>IF($E14=H$1,$D14*M$2/1000*$A14, "")</f>
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <f>IF($E14=I$1,$D14*N$2/1000*$A14, "")</f>
+        <v/>
+      </c>
+      <c r="J14">
+        <f>IF($E14=J$1,$D14*O$2/1000*$A14, "")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" t="str">
+        <f>IF($E15=G$1,$D15*L$2/1000*$A15, "")</f>
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <f>IF($E15=H$1,$D15*M$2/1000*$A15, "")</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF($E15=I$1,$D15*N$2/1000*$A15, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J15" t="str">
+        <f>IF($E15=J$1,$D15*O$2/1000*$A15, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" t="str">
+        <f>IF($E16=G$1,$D16*L$2/1000*$A16, "")</f>
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <f>IF($E16=H$1,$D16*M$2/1000*$A16, "")</f>
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <f>IF($E16=I$1,$D16*N$2/1000*$A16, "")</f>
+        <v/>
+      </c>
+      <c r="J16">
+        <f>IF($E16=J$1,$D16*O$2/1000*$A16, "")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" t="str">
+        <f>IF($E17=G$1,$D17*L$2/1000*$A17, "")</f>
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <f>IF($E17=H$1,$D17*M$2/1000*$A17, "")</f>
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <f>IF($E17=I$1,$D17*N$2/1000*$A17, "")</f>
+        <v/>
+      </c>
+      <c r="J17">
+        <f>IF($E17=J$1,$D17*O$2/1000*$A17, "")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" t="str">
+        <f>IF($E18=G$1,$D18*L$2/1000*$A18, "")</f>
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <f>IF($E18=H$1,$D18*M$2/1000*$A18, "")</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF($E18=I$1,$D18*N$2/1000*$A18, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J18" t="str">
+        <f>IF($E18=J$1,$D18*O$2/1000*$A18, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="G19" t="str">
+        <f>IF($E19=G$1,$D19*L$2/1000*$A19, "")</f>
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <f>IF($E19=H$1,$D19*M$2/1000*$A19, "")</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF($E19=I$1,$D19*N$2/1000*$A19, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J19" t="str">
+        <f>IF($E19=J$1,$D19*O$2/1000*$A19, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" t="str">
+        <f>IF($E20=G$1,$D20*L$2/1000*$A20, "")</f>
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <f>IF($E20=H$1,$D20*M$2/1000*$A20, "")</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF($E20=I$1,$D20*N$2/1000*$A20, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J20" t="str">
+        <f>IF($E20=J$1,$D20*O$2/1000*$A20, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF($E21=G$1,$D21*L$2/1000*$A21, "")</f>
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <f>IF($E21=H$1,$D21*M$2/1000*$A21, "")</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF($E21=I$1,$D21*N$2/1000*$A21, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J21" t="str">
+        <f>IF($E21=J$1,$D21*O$2/1000*$A21, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" t="str">
+        <f>IF($E22=G$1,$D22*L$2/1000*$A22, "")</f>
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <f>IF($E22=H$1,$D22*M$2/1000*$A22, "")</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF($E22=I$1,$D22*N$2/1000*$A22, "")</f>
+        <v>0</v>
+      </c>
+      <c r="J22" t="str">
+        <f>IF($E22=J$1,$D22*O$2/1000*$A22, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G23" t="str">
+        <f>IF($E23=G$1,$D23*L$2/1000*$A23, "")</f>
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <f>IF($E23=H$1,$D23*M$2/1000*$A23, "")</f>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <f>IF($E23=I$1,$D23*N$2/1000*$A23, "")</f>
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <f>IF($E23=J$1,$D23*O$2/1000*$A23, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G24" t="str">
+        <f>IF($E24=G$1,$D24*L$2/1000*$A24, "")</f>
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <f>IF($E24=H$1,$D24*M$2/1000*$A24, "")</f>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <f>IF($E24=I$1,$D24*N$2/1000*$A24, "")</f>
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <f>IF($E24=J$1,$D24*O$2/1000*$A24, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G25" t="str">
+        <f>IF($E25=G$1,$D25*L$2/1000*$A25, "")</f>
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <f>IF($E25=H$1,$D25*M$2/1000*$A25, "")</f>
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <f>IF($E25=I$1,$D25*N$2/1000*$A25, "")</f>
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <f>IF($E25=J$1,$D25*O$2/1000*$A25, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G26" t="str">
+        <f>IF($E26=G$1,$D26*L$2/1000*$A26, "")</f>
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <f>IF($E26=H$1,$D26*M$2/1000*$A26, "")</f>
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <f>IF($E26=I$1,$D26*N$2/1000*$A26, "")</f>
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <f>IF($E26=J$1,$D26*O$2/1000*$A26, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G27" t="str">
+        <f>IF($E27=G$1,$D27*L$2/1000*$A27, "")</f>
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <f>IF($E27=H$1,$D27*M$2/1000*$A27, "")</f>
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <f>IF($E27=I$1,$D27*N$2/1000*$A27, "")</f>
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <f>IF($E27=J$1,$D27*O$2/1000*$A27, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G28" t="str">
+        <f>IF($E28=G$1,$D28*L$2/1000*$A28, "")</f>
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <f>IF($E28=H$1,$D28*M$2/1000*$A28, "")</f>
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <f>IF($E28=I$1,$D28*N$2/1000*$A28, "")</f>
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <f>IF($E28=J$1,$D28*O$2/1000*$A28, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G29" t="str">
+        <f>IF($E29=G$1,$D29*L$2/1000*$A29, "")</f>
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <f>IF($E29=H$1,$D29*M$2/1000*$A29, "")</f>
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <f>IF($E29=I$1,$D29*N$2/1000*$A29, "")</f>
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <f>IF($E29=J$1,$D29*O$2/1000*$A29, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G30" t="str">
+        <f>IF($E30=G$1,$D30*L$2/1000*$A30, "")</f>
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <f>IF($E30=H$1,$D30*M$2/1000*$A30, "")</f>
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <f>IF($E30=I$1,$D30*N$2/1000*$A30, "")</f>
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <f>IF($E30=J$1,$D30*O$2/1000*$A30, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G31" t="str">
+        <f>IF($E31=G$1,$D31*L$2/1000*$A31, "")</f>
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <f>IF($E31=H$1,$D31*M$2/1000*$A31, "")</f>
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <f>IF($E31=I$1,$D31*N$2/1000*$A31, "")</f>
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <f>IF($E31=J$1,$D31*O$2/1000*$A31, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G32" t="str">
+        <f>IF($E32=G$1,$D32*L$2/1000*$A32, "")</f>
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <f>IF($E32=H$1,$D32*M$2/1000*$A32, "")</f>
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <f>IF($E32=I$1,$D32*N$2/1000*$A32, "")</f>
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <f>IF($E32=J$1,$D32*O$2/1000*$A32, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G33" t="str">
+        <f>IF($E33=G$1,$D33*L$2/1000*$A33, "")</f>
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <f>IF($E33=H$1,$D33*M$2/1000*$A33, "")</f>
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <f>IF($E33=I$1,$D33*N$2/1000*$A33, "")</f>
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <f>IF($E33=J$1,$D33*O$2/1000*$A33, "")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G34" t="str">
+        <f>IF($E34=G$1,$D34*L$2/1000*$A34, "")</f>
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <f>IF($E34=H$1,$D34*M$2/1000*$A34, "")</f>
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <f>IF($E34=I$1,$D34*N$2/1000*$A34, "")</f>
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <f>IF($E34=J$1,$D34*O$2/1000*$A34, "")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:C66"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="12"/>
+    <col min="2" max="2" width="37.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="12"/>
+    <col min="4" max="16384" width="9.140625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="19">
+        <v>1.59</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="21">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="21">
+        <v>87.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" s="19">
+        <v>1.61</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="21">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
+        <v>1.62</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="21">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
+        <v>1.63</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="21">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
+        <v>1.64</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="21">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="19">
+        <v>1.65</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="21">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="19">
+        <v>1.66</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="21">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="19">
+        <v>1.67</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="19">
+        <v>1.68</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="21">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="19">
+        <v>1.69</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="19">
+        <v>1.7</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="21">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="19">
+        <v>1.71</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="21">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
+        <v>1.72</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="21">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="19">
+        <v>1.73</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="21">
+        <v>50.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="19">
+        <v>1.74</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="21">
+        <v>55.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="19">
+        <v>1.75</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="21">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="19">
+        <v>1.76</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="21">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="19">
+        <v>1.77</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="21">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="19">
+        <v>1.78</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="21">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="18"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="18"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="18">
+        <v>2.36</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="18">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="18">
+        <v>2.37</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="18">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="18">
+        <v>2.38</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="18">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="18">
+        <v>2.39</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="18">
+        <v>2.4</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="18">
+        <v>50.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="18">
+        <v>2.41</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="18">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="18">
+        <v>2.42</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="18">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C29" s="18">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="18">
+        <v>2.44</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="18">
+        <v>50.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="18">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="18">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="18">
+        <v>2.46</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="18">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="18">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="18">
+        <v>2.48</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" s="18">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="18">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="18">
+        <v>72.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="18">
+        <v>2.5</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="18">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="18">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="18">
+        <v>2.52</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="18">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="18">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="18">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="18">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="18">
+        <v>2.56</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="18">
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="18">
+        <v>2.57</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="18">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="18">
+        <v>2.58</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="18">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="18"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="18"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="18">
+        <v>3.22</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C45" s="18">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="18">
+        <v>3.23</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="18">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="18">
+        <v>3.24</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="18">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="18">
+        <v>3.25</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="18">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="18">
+        <v>3.26</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="18">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="18">
+        <v>3.27</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C50" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="18">
+        <v>3.28</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="18">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="18">
+        <v>3.29</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="18">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="18">
+        <v>3.3</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="18">
+        <v>55.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="18">
+        <v>3.31</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="18">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="18">
+        <v>3.32</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A56" s="18">
+        <v>3.33</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="18">
+        <v>74.599999999999994</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="18">
+        <v>3.34</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="18">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A58" s="18">
+        <v>3.35</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="18">
+        <v>74.099999999999994</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A59" s="18">
+        <v>3.36</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="18">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="18">
+        <v>3.37</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60" s="18">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="18">
+        <v>3.39</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" s="18">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="18">
+        <v>3.4</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="18">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="18">
+        <v>3.41</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="18">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="18">
+        <v>3.42</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="18">
+        <v>59.7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="18">
+        <v>3.44</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="18">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="18">
+        <v>3.45</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="18">
+        <v>82.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3722,7 +4818,7 @@
       </c>
       <c r="C4" s="21"/>
       <c r="D4" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="17">
         <f t="shared" ref="E4:E9" si="0">C4*2.19</f>
@@ -3730,11 +4826,11 @@
       </c>
       <c r="F4" s="17">
         <f t="shared" ref="F4:F9" si="1">D4*1.47</f>
-        <v>1.47</v>
+        <v>2.94</v>
       </c>
       <c r="G4" s="17">
         <f t="shared" ref="G4:G9" si="2">SUM(E4:F4)</f>
-        <v>1.47</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -4315,55 +5411,1618 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A10"/>
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="37.28515625" customWidth="1"/>
+    <col min="3" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="D1" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="H1" s="25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
+        <v>1.59</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="C2" s="27"/>
+      <c r="D2" s="26">
+        <v>48.8914008</v>
+      </c>
+      <c r="E2" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="F2" s="26">
+        <v>5.5650000000000004</v>
+      </c>
+      <c r="G2" s="26">
+        <v>0</v>
+      </c>
+      <c r="H2" s="26">
+        <f>ROUND(D2-E2-F2-G2, 2)</f>
+        <v>41.12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
+        <v>1.6</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="27"/>
+      <c r="D3" s="26">
+        <v>125.36737767300001</v>
+      </c>
+      <c r="E3" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F3" s="26">
+        <v>4.3049999999999997</v>
+      </c>
+      <c r="G3" s="26">
+        <v>0</v>
+      </c>
+      <c r="H3" s="26">
+        <f t="shared" ref="H3:H65" si="0">ROUND(D3-E3-F3-G3, 2)</f>
+        <v>109.81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
+        <v>1.61</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="27"/>
+      <c r="D4" s="26">
+        <v>66.716409014999996</v>
+      </c>
+      <c r="E4" s="26">
+        <v>4.9050000000000002</v>
+      </c>
+      <c r="F4" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0</v>
+      </c>
+      <c r="H4" s="26">
+        <f t="shared" si="0"/>
+        <v>59.82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
+        <v>1.62</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="27"/>
+      <c r="D5" s="26">
+        <v>38.498279607000001</v>
+      </c>
+      <c r="E5" s="26">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G5" s="26">
+        <v>0</v>
+      </c>
+      <c r="H5" s="26">
+        <f t="shared" si="0"/>
+        <v>36.19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>1.63</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>3</v>
-      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="26">
+        <v>23.623230786000001</v>
+      </c>
+      <c r="E6" s="26">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G6" s="26">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26">
+        <f t="shared" si="0"/>
+        <v>20.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>1.64</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="27"/>
+      <c r="D7" s="26">
+        <v>98.297160000000005</v>
+      </c>
+      <c r="E7" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F7" s="26">
+        <v>8.82</v>
+      </c>
+      <c r="G7" s="26">
+        <v>0</v>
+      </c>
+      <c r="H7" s="26">
+        <f t="shared" si="0"/>
+        <v>87.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>1.65</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="26">
+        <v>42.459720000000004</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26">
+        <v>3.99</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26">
+        <f t="shared" si="0"/>
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>1.66</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="27"/>
+      <c r="D9" s="26">
+        <v>88.543935162000011</v>
+      </c>
+      <c r="E9" s="26">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G9" s="26">
+        <v>0</v>
+      </c>
+      <c r="H9" s="26">
+        <f t="shared" si="0"/>
+        <v>86.34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>1.67</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="27"/>
+      <c r="D10" s="26">
+        <v>107.02962589500001</v>
+      </c>
+      <c r="E10" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F10" s="26">
+        <v>7.14</v>
+      </c>
+      <c r="G10" s="26">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26">
+        <f t="shared" si="0"/>
+        <v>88.64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>1.68</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="27"/>
+      <c r="D11" s="26">
+        <v>103.614568293</v>
+      </c>
+      <c r="E11" s="26">
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="F11" s="26">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26">
+        <f t="shared" si="0"/>
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>1.69</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="26">
+        <v>80.486399606999996</v>
+      </c>
+      <c r="E12" s="26">
+        <v>0</v>
+      </c>
+      <c r="F12" s="26">
+        <v>8.82</v>
+      </c>
+      <c r="G12" s="26">
+        <v>0</v>
+      </c>
+      <c r="H12" s="26">
+        <f t="shared" si="0"/>
+        <v>71.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>1.7</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="27"/>
+      <c r="D13" s="26">
+        <v>34.741199607000006</v>
+      </c>
+      <c r="E13" s="26">
+        <v>0</v>
+      </c>
+      <c r="F13" s="26">
+        <v>5.9849999999999994</v>
+      </c>
+      <c r="G13" s="26">
+        <v>0</v>
+      </c>
+      <c r="H13" s="26">
+        <f t="shared" si="0"/>
+        <v>28.76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>1.71</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="27"/>
+      <c r="D14" s="26">
+        <v>98.800199606999996</v>
+      </c>
+      <c r="E14" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F14" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0</v>
+      </c>
+      <c r="H14" s="26">
+        <f t="shared" si="0"/>
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>1.72</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C15" s="27"/>
+      <c r="D15" s="26">
+        <v>90.075600393000016</v>
+      </c>
+      <c r="E15" s="26">
+        <v>0</v>
+      </c>
+      <c r="F15" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0</v>
+      </c>
+      <c r="H15" s="26">
+        <f t="shared" si="0"/>
+        <v>87.87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>1.73</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="26">
+        <v>106.32627968999999</v>
+      </c>
+      <c r="E16" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F16" s="26">
+        <v>7.14</v>
+      </c>
+      <c r="G16" s="26">
+        <v>0</v>
+      </c>
+      <c r="H16" s="26">
+        <f t="shared" si="0"/>
+        <v>87.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
+        <v>1.74</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="27"/>
+      <c r="D17" s="26">
+        <v>103.551650958</v>
+      </c>
+      <c r="E17" s="26">
+        <v>9.8999999999999986</v>
+      </c>
+      <c r="F17" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G17" s="26">
+        <v>0</v>
+      </c>
+      <c r="H17" s="26">
+        <f t="shared" si="0"/>
+        <v>90.71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
+        <v>1.75</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="26">
+        <v>46.079151357000001</v>
+      </c>
+      <c r="E18" s="26">
+        <v>0</v>
+      </c>
+      <c r="F18" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G18" s="26">
+        <v>0</v>
+      </c>
+      <c r="H18" s="26">
+        <f t="shared" si="0"/>
+        <v>44.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
+        <v>1.76</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="26">
+        <v>84.63230398200001</v>
+      </c>
+      <c r="E19" s="26">
+        <v>0</v>
+      </c>
+      <c r="F19" s="26">
+        <v>9.9750000000000014</v>
+      </c>
+      <c r="G19" s="26">
+        <v>0</v>
+      </c>
+      <c r="H19" s="26">
+        <f t="shared" si="0"/>
+        <v>74.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
+        <v>1.77</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="27"/>
+      <c r="D20" s="26">
+        <v>100.013001144</v>
+      </c>
+      <c r="E20" s="26">
+        <v>0</v>
+      </c>
+      <c r="F20" s="26">
+        <v>16.8</v>
+      </c>
+      <c r="G20" s="26">
+        <v>5.04</v>
+      </c>
+      <c r="H20" s="26">
+        <f t="shared" si="0"/>
+        <v>78.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="19">
+        <v>1.78</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="26">
+        <v>144.694936893</v>
+      </c>
+      <c r="E21" s="26">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26">
+        <v>10.92</v>
+      </c>
+      <c r="G21" s="26">
+        <v>1.26</v>
+      </c>
+      <c r="H21" s="26">
+        <f t="shared" si="0"/>
+        <v>132.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="24">
+        <v>2.36</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="26">
+        <v>49.642459170000002</v>
+      </c>
+      <c r="E23" s="26">
+        <v>0</v>
+      </c>
+      <c r="F23" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G23" s="26">
+        <v>0</v>
+      </c>
+      <c r="H23" s="26">
+        <f t="shared" si="0"/>
+        <v>47.65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="24">
+        <v>2.37</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="26">
+        <v>98.297160000000005</v>
+      </c>
+      <c r="E24" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F24" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G24" s="26">
+        <v>0</v>
+      </c>
+      <c r="H24" s="26">
+        <f t="shared" si="0"/>
+        <v>90.39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="24">
+        <v>2.38</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="26">
+        <v>42.459720000000004</v>
+      </c>
+      <c r="E25" s="26">
+        <v>0</v>
+      </c>
+      <c r="F25" s="26">
+        <v>3.99</v>
+      </c>
+      <c r="G25" s="26">
+        <v>0</v>
+      </c>
+      <c r="H25" s="26">
+        <f t="shared" si="0"/>
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="24">
+        <v>2.39</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="28"/>
+      <c r="D26" s="26">
+        <v>88.543935162000011</v>
+      </c>
+      <c r="E26" s="26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G26" s="26">
+        <v>0</v>
+      </c>
+      <c r="H26" s="26">
+        <f t="shared" si="0"/>
+        <v>86.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="24">
+        <v>2.4</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="28"/>
+      <c r="D27" s="26">
+        <v>107.02962589500001</v>
+      </c>
+      <c r="E27" s="26">
+        <v>6.0749999999999993</v>
+      </c>
+      <c r="F27" s="26">
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="G27" s="26">
+        <v>0</v>
+      </c>
+      <c r="H27" s="26">
+        <f t="shared" si="0"/>
+        <v>93.81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="24">
+        <v>2.41</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="28"/>
+      <c r="D28" s="26">
+        <v>103.614568293</v>
+      </c>
+      <c r="E28" s="26">
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="F28" s="26">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="G28" s="26">
+        <v>0</v>
+      </c>
+      <c r="H28" s="26">
+        <f t="shared" si="0"/>
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="24">
+        <v>2.42</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="26">
+        <v>98.800199606999996</v>
+      </c>
+      <c r="E29" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F29" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G29" s="26">
+        <v>0</v>
+      </c>
+      <c r="H29" s="26">
+        <f t="shared" si="0"/>
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="24">
+        <v>2.4300000000000002</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="26">
+        <v>43.23</v>
+      </c>
+      <c r="E30" s="26">
+        <v>0</v>
+      </c>
+      <c r="F30" s="26">
+        <v>3.99</v>
+      </c>
+      <c r="G30" s="26">
+        <v>0</v>
+      </c>
+      <c r="H30" s="26">
+        <f t="shared" si="0"/>
+        <v>39.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="24">
+        <v>2.44</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="26">
+        <v>106.32627968999999</v>
+      </c>
+      <c r="E31" s="26">
+        <v>12.375</v>
+      </c>
+      <c r="F31" s="26">
+        <v>7.1400000000000006</v>
+      </c>
+      <c r="G31" s="26">
+        <v>0</v>
+      </c>
+      <c r="H31" s="26">
+        <f t="shared" si="0"/>
+        <v>86.81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="24">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="26">
+        <v>103.551650958</v>
+      </c>
+      <c r="E32" s="26">
+        <v>8.7749999999999986</v>
+      </c>
+      <c r="F32" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G32" s="26">
+        <v>0</v>
+      </c>
+      <c r="H32" s="26">
+        <f t="shared" si="0"/>
+        <v>91.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="24">
+        <v>2.46</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="26">
+        <v>90.075600393000016</v>
+      </c>
+      <c r="E33" s="26">
+        <v>0</v>
+      </c>
+      <c r="F33" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G33" s="26">
+        <v>0</v>
+      </c>
+      <c r="H33" s="26">
+        <f t="shared" si="0"/>
+        <v>87.87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="39" x14ac:dyDescent="0.25">
+      <c r="A34" s="24">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C34" s="28"/>
+      <c r="D34" s="26">
+        <v>153.33546594000003</v>
+      </c>
+      <c r="E34" s="26">
+        <v>11.925000000000001</v>
+      </c>
+      <c r="F34" s="26">
+        <v>8.1795000000000009</v>
+      </c>
+      <c r="G34" s="26">
+        <v>0</v>
+      </c>
+      <c r="H34" s="26">
+        <f t="shared" si="0"/>
+        <v>133.22999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A35" s="24">
+        <v>2.48</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="26">
+        <v>42.329278977000001</v>
+      </c>
+      <c r="E35" s="26">
+        <v>0</v>
+      </c>
+      <c r="F35" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G35" s="26">
+        <v>0</v>
+      </c>
+      <c r="H35" s="26">
+        <f t="shared" si="0"/>
+        <v>40.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="24">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="28"/>
+      <c r="D36" s="26">
+        <v>147.206162484</v>
+      </c>
+      <c r="E36" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F36" s="26">
+        <v>5.5754999999999999</v>
+      </c>
+      <c r="G36" s="26">
+        <v>0</v>
+      </c>
+      <c r="H36" s="26">
+        <f t="shared" si="0"/>
+        <v>130.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="26">
+        <v>41.295226023000005</v>
+      </c>
+      <c r="E37" s="26">
+        <v>0</v>
+      </c>
+      <c r="F37" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G37" s="26">
+        <v>0</v>
+      </c>
+      <c r="H37" s="26">
+        <f t="shared" si="0"/>
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="24">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="28"/>
+      <c r="D38" s="26">
+        <v>104.52963971100002</v>
+      </c>
+      <c r="E38" s="26">
+        <v>0</v>
+      </c>
+      <c r="F38" s="26">
+        <v>17.43</v>
+      </c>
+      <c r="G38" s="26">
+        <v>5.04</v>
+      </c>
+      <c r="H38" s="26">
+        <f t="shared" si="0"/>
+        <v>82.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="24">
+        <v>2.52</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="28"/>
+      <c r="D39" s="26">
+        <v>40.767565359000002</v>
+      </c>
+      <c r="E39" s="26">
+        <v>0</v>
+      </c>
+      <c r="F39" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G39" s="26">
+        <v>0</v>
+      </c>
+      <c r="H39" s="26">
+        <f t="shared" si="0"/>
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="24">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="28"/>
+      <c r="D40" s="26">
+        <v>40.599155034000006</v>
+      </c>
+      <c r="E40" s="26">
+        <v>0</v>
+      </c>
+      <c r="F40" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G40" s="26">
+        <v>0</v>
+      </c>
+      <c r="H40" s="26">
+        <f t="shared" si="0"/>
+        <v>38.29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="24">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="28"/>
+      <c r="D41" s="26">
+        <v>44.220359999999999</v>
+      </c>
+      <c r="E41" s="26">
+        <v>0</v>
+      </c>
+      <c r="F41" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G41" s="26">
+        <v>0</v>
+      </c>
+      <c r="H41" s="26">
+        <f t="shared" si="0"/>
+        <v>41.28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="24">
+        <v>2.56</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="28"/>
+      <c r="D42" s="26">
+        <v>190.821736749</v>
+      </c>
+      <c r="E42" s="26">
+        <v>0</v>
+      </c>
+      <c r="F42" s="26">
+        <v>20.369999999999997</v>
+      </c>
+      <c r="G42" s="26">
+        <v>0</v>
+      </c>
+      <c r="H42" s="26">
+        <f t="shared" si="0"/>
+        <v>170.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="24">
+        <v>2.57</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="28"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="24">
+        <v>2.58</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="28"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="24">
+        <v>3.22</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C46" s="28"/>
+      <c r="D46" s="26">
+        <v>49.642459170000002</v>
+      </c>
+      <c r="E46" s="26">
+        <v>0</v>
+      </c>
+      <c r="F46" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G46" s="26">
+        <v>0</v>
+      </c>
+      <c r="H46" s="26">
+        <f t="shared" si="0"/>
+        <v>47.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="24">
+        <v>3.23</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="28"/>
+      <c r="D47" s="26">
+        <v>98.297160000000005</v>
+      </c>
+      <c r="E47" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F47" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G47" s="26">
+        <v>0</v>
+      </c>
+      <c r="H47" s="26">
+        <f t="shared" si="0"/>
+        <v>90.39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="24">
+        <v>3.24</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="28"/>
+      <c r="D48" s="26">
+        <v>42.459720000000004</v>
+      </c>
+      <c r="E48" s="26">
+        <v>0</v>
+      </c>
+      <c r="F48" s="26">
+        <v>3.99</v>
+      </c>
+      <c r="G48" s="26">
+        <v>0</v>
+      </c>
+      <c r="H48" s="26">
+        <f t="shared" si="0"/>
+        <v>38.47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="24">
+        <v>3.25</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" s="28"/>
+      <c r="D49" s="26">
+        <v>107.02962589500001</v>
+      </c>
+      <c r="E49" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F49" s="26">
+        <v>7.14</v>
+      </c>
+      <c r="G49" s="26">
+        <v>0</v>
+      </c>
+      <c r="H49" s="26">
+        <f t="shared" si="0"/>
+        <v>88.64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="24">
+        <v>3.26</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="28"/>
+      <c r="D50" s="26">
+        <v>103.614568293</v>
+      </c>
+      <c r="E50" s="26">
+        <v>7.1999999999999993</v>
+      </c>
+      <c r="F50" s="26">
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="G50" s="26">
+        <v>0</v>
+      </c>
+      <c r="H50" s="26">
+        <f t="shared" si="0"/>
+        <v>93.37</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="24">
+        <v>3.27</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C51" s="28"/>
+      <c r="D51" s="26">
+        <v>88.543935162000011</v>
+      </c>
+      <c r="E51" s="26">
+        <v>0</v>
+      </c>
+      <c r="F51" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G51" s="26">
+        <v>0</v>
+      </c>
+      <c r="H51" s="26">
+        <f t="shared" si="0"/>
+        <v>86.34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="24">
+        <v>3.28</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="28"/>
+      <c r="D52" s="26">
+        <v>98.800199606999996</v>
+      </c>
+      <c r="E52" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F52" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G52" s="26">
+        <v>0</v>
+      </c>
+      <c r="H52" s="26">
+        <f t="shared" si="0"/>
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="24">
+        <v>3.29</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" s="28"/>
+      <c r="D53" s="26">
+        <v>106.32627968999999</v>
+      </c>
+      <c r="E53" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F53" s="26">
+        <v>7.14</v>
+      </c>
+      <c r="G53" s="26">
+        <v>0</v>
+      </c>
+      <c r="H53" s="26">
+        <f t="shared" si="0"/>
+        <v>87.94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="24">
+        <v>3.3</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" s="28"/>
+      <c r="D54" s="26">
+        <v>103.551650958</v>
+      </c>
+      <c r="E54" s="26">
+        <v>9.8999999999999986</v>
+      </c>
+      <c r="F54" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G54" s="26">
+        <v>0</v>
+      </c>
+      <c r="H54" s="26">
+        <f t="shared" si="0"/>
+        <v>90.71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="24">
+        <v>3.31</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55" s="28"/>
+      <c r="D55" s="26">
+        <v>98.800199606999996</v>
+      </c>
+      <c r="E55" s="26">
+        <v>2.0249999999999999</v>
+      </c>
+      <c r="F55" s="26">
+        <v>5.88</v>
+      </c>
+      <c r="G55" s="26">
+        <v>0</v>
+      </c>
+      <c r="H55" s="26">
+        <f t="shared" si="0"/>
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="24">
+        <v>3.32</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="28"/>
+      <c r="D56" s="26">
+        <v>90.075600393000016</v>
+      </c>
+      <c r="E56" s="26">
+        <v>0</v>
+      </c>
+      <c r="F56" s="26">
+        <v>2.2050000000000001</v>
+      </c>
+      <c r="G56" s="26">
+        <v>0</v>
+      </c>
+      <c r="H56" s="26">
+        <f t="shared" si="0"/>
+        <v>87.87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="39" x14ac:dyDescent="0.25">
+      <c r="A57" s="24">
+        <v>3.33</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57" s="28"/>
+      <c r="D57" s="26">
+        <v>148.548967242</v>
+      </c>
+      <c r="E57" s="26">
+        <v>12.442500000000001</v>
+      </c>
+      <c r="F57" s="26">
+        <v>5.04</v>
+      </c>
+      <c r="G57" s="26">
+        <v>0</v>
+      </c>
+      <c r="H57" s="26">
+        <f t="shared" si="0"/>
+        <v>131.07</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="24">
+        <v>3.34</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C58" s="28"/>
+      <c r="D58" s="26">
+        <v>42.167083947000002</v>
+      </c>
+      <c r="E58" s="26">
+        <v>0</v>
+      </c>
+      <c r="F58" s="26">
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="G58" s="26">
+        <v>0</v>
+      </c>
+      <c r="H58" s="26">
+        <f t="shared" si="0"/>
+        <v>40.17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="39" x14ac:dyDescent="0.25">
+      <c r="A59" s="24">
+        <v>3.35</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="28"/>
+      <c r="D59" s="26">
+        <v>142.01463916500003</v>
+      </c>
+      <c r="E59" s="26">
+        <v>11.25</v>
+      </c>
+      <c r="F59" s="26">
+        <v>8.6204999999999998</v>
+      </c>
+      <c r="G59" s="26">
+        <v>0</v>
+      </c>
+      <c r="H59" s="26">
+        <f t="shared" si="0"/>
+        <v>122.14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A60" s="24">
+        <v>3.36</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="28"/>
+      <c r="D60" s="26">
+        <v>40.137596970000004</v>
+      </c>
+      <c r="E60" s="26">
+        <v>0</v>
+      </c>
+      <c r="F60" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G60" s="26">
+        <v>0</v>
+      </c>
+      <c r="H60" s="26">
+        <f t="shared" si="0"/>
+        <v>37.83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="24">
+        <v>3.37</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="28"/>
+      <c r="D61" s="26">
+        <v>40.380751572000008</v>
+      </c>
+      <c r="E61" s="26">
+        <v>0</v>
+      </c>
+      <c r="F61" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G61" s="26">
+        <v>0</v>
+      </c>
+      <c r="H61" s="26">
+        <f t="shared" si="0"/>
+        <v>38.07</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="24">
+        <v>3.39</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C62" s="28"/>
+      <c r="D62" s="26">
+        <v>44.216434323000001</v>
+      </c>
+      <c r="E62" s="26">
+        <v>0</v>
+      </c>
+      <c r="F62" s="26">
+        <v>2.94</v>
+      </c>
+      <c r="G62" s="26">
+        <v>0</v>
+      </c>
+      <c r="H62" s="26">
+        <f t="shared" si="0"/>
+        <v>41.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="24">
+        <v>3.4</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="28"/>
+      <c r="D63" s="26">
+        <v>41.861939097000004</v>
+      </c>
+      <c r="E63" s="26">
+        <v>0</v>
+      </c>
+      <c r="F63" s="26">
+        <v>2.31</v>
+      </c>
+      <c r="G63" s="26">
+        <v>0</v>
+      </c>
+      <c r="H63" s="26">
+        <f t="shared" si="0"/>
+        <v>39.549999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="24">
+        <v>3.41</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="28"/>
+      <c r="D64" s="26">
+        <v>104.67865234200002</v>
+      </c>
+      <c r="E64" s="26">
+        <v>0</v>
+      </c>
+      <c r="F64" s="26">
+        <v>17.43</v>
+      </c>
+      <c r="G64" s="26">
+        <v>5.04</v>
+      </c>
+      <c r="H64" s="26">
+        <f t="shared" si="0"/>
+        <v>82.21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="24">
+        <v>3.42</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="28"/>
+      <c r="D65" s="26">
+        <v>190.91155965000002</v>
+      </c>
+      <c r="E65" s="26">
+        <v>0</v>
+      </c>
+      <c r="F65" s="26">
+        <v>20.275500000000001</v>
+      </c>
+      <c r="G65" s="26">
+        <v>0</v>
+      </c>
+      <c r="H65" s="26">
+        <f t="shared" si="0"/>
+        <v>170.64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="24">
+        <v>3.44</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="28"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="24">
+        <v>3.45</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="28"/>
+      <c r="D67" s="26"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
